--- a/public/sap-reporting/expansion-150-downloads/EXT-CO29-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-CO29-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Re573623810e746dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Re71019092fb7416a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R6a0642008f4c443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R37d54fbbbf8840c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rfb6ec64ac9f448f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R3408d8954f78497a"/>
   </x:sheets>
 </x:workbook>
 </file>
